--- a/product_selector_out/STM32U0 series.xlsx
+++ b/product_selector_out/STM32U0 series.xlsx
@@ -21981,7 +21981,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22069,7 +22069,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22333,7 +22333,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22531,7 +22531,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22773,7 +22773,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22949,7 +22949,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23081,7 +23081,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23169,7 +23169,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23499,7 +23499,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23565,7 +23565,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23653,7 +23653,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23829,7 +23829,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23917,7 +23917,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24005,7 +24005,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24071,7 +24071,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24181,7 +24181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24357,7 +24357,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24511,7 +24511,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32U0 series.xlsx
+++ b/product_selector_out/STM32U0 series.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2714,7 +2720,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -3041,7 +3047,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
@@ -3368,7 +3374,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -3695,7 +3701,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -5984,7 +5990,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S27" s="4" t="inlineStr">
@@ -6311,7 +6317,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S28" s="4" t="inlineStr">
@@ -7619,7 +7625,7 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
@@ -7946,12 +7952,12 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr">
@@ -8273,12 +8279,12 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T34" s="4" t="inlineStr">
@@ -8600,7 +8606,7 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S35" s="4" t="inlineStr">
@@ -8927,7 +8933,7 @@
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S36" s="4" t="inlineStr">
@@ -9581,12 +9587,12 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T38" s="4" t="inlineStr">
@@ -9908,7 +9914,7 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S39" s="4" t="inlineStr">
@@ -10235,7 +10241,7 @@
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S40" s="4" t="inlineStr">
@@ -13457,14 +13463,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T17" s="9" t="inlineStr">
@@ -13784,14 +13790,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T18" s="9" t="inlineStr">
@@ -14111,14 +14117,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T19" s="9" t="inlineStr">
@@ -14438,14 +14444,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T20" s="9" t="inlineStr">
@@ -16727,14 +16733,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T27" s="9" t="inlineStr">
@@ -17054,14 +17060,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T28" s="9" t="inlineStr">
@@ -18362,14 +18368,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R32" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T32" s="9" t="inlineStr">
@@ -18689,14 +18695,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T33" s="9" t="inlineStr">
@@ -19016,14 +19022,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R34" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T34" s="9" t="inlineStr">
@@ -19343,14 +19349,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T35" s="9" t="inlineStr">
@@ -19670,14 +19676,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R36" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T36" s="9" t="inlineStr">
@@ -20324,14 +20330,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R38" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T38" s="9" t="inlineStr">
@@ -20651,14 +20657,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T39" s="9" t="inlineStr">
@@ -20978,14 +20984,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R40" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T40" s="9" t="inlineStr">
@@ -21888,7 +21894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22367,7 +22373,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -22377,7 +22383,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
@@ -22389,7 +22395,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -22399,14 +22405,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U073R8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -22428,7 +22434,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U073R8</t>
+          <t>STM32U073MB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -22450,12 +22456,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -22465,19 +22471,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073M8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -22487,14 +22493,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -22516,7 +22522,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U073MB</t>
+          <t>STM32U073RB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -22538,7 +22544,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -22553,14 +22559,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -22575,19 +22581,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -22597,19 +22603,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U073M8</t>
+          <t>STM32U031K8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -22619,14 +22625,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -22641,14 +22647,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -22663,19 +22669,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -22685,19 +22691,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U073RB</t>
+          <t>STM32U031F8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -22707,14 +22713,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U083HC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -22736,7 +22742,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U083HC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -22758,7 +22764,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U083HC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22773,19 +22779,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U031K8</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -22795,19 +22801,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -22824,12 +22830,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U083CC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -22839,19 +22845,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -22861,19 +22867,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U031F8</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -22883,19 +22889,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U083HC</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -22905,19 +22911,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U083HC</t>
+          <t>STM32U031K4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -22927,19 +22933,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U083HC</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -22949,19 +22955,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -22978,12 +22984,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -22993,19 +22999,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U083CC</t>
+          <t>STM32U031K6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -23015,19 +23021,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -23037,19 +23043,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073CB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -23059,19 +23065,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -23081,19 +23087,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U031K4</t>
+          <t>STM32U073C8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -23103,14 +23109,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -23132,7 +23138,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -23154,7 +23160,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083MC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -23169,19 +23175,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U031K6</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -23191,19 +23197,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -23213,19 +23219,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083RC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -23235,19 +23241,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -23257,19 +23263,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U073CB</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -23279,19 +23285,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U083KC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -23301,19 +23307,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -23323,19 +23329,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073KC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -23345,19 +23351,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U073C8</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -23367,19 +23373,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U073K8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -23389,19 +23395,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -23411,14 +23417,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U083MC</t>
+          <t>STM32U073CC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -23440,12 +23446,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -23455,19 +23461,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073RC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -23477,19 +23483,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U083RC</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -23499,19 +23505,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U073MC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -23521,19 +23527,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U031G6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -23550,12 +23556,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U083KC</t>
+          <t>STM32U031G6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -23565,19 +23571,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U031G6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -23587,19 +23593,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U031G6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -23609,14 +23615,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -23638,7 +23644,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U073KC</t>
+          <t>STM32U073KB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -23660,12 +23666,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073H8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -23675,19 +23681,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073H8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -23697,14 +23703,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073HB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -23726,7 +23732,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U073K8</t>
+          <t>STM32U073HB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -23748,7 +23754,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U031C6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -23763,14 +23769,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U031C6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -23785,19 +23791,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U031C6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -23807,19 +23813,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U073CC</t>
+          <t>STM32U031C6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -23829,14 +23835,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U031G8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -23851,14 +23857,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U031G8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -23873,19 +23879,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U031G8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -23895,19 +23901,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U073RC</t>
+          <t>STM32U031G8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -23916,622 +23922,6 @@
         </is>
       </c>
       <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32U073MC</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32U031G6</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32U031G6</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32U031G6</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32U031G6</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32U073KB</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32U073H8</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Table 1. Device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32U073HB</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32U031C6</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32U031C6</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32U031C6</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32U031C6</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32U031G8</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32U031G8</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32U031G8</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32U031G8</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes, code with data processing running from flash memory, bypass mode, ART enabled</t>
         </is>

--- a/product_selector_out/STM32U0 series.xlsx
+++ b/product_selector_out/STM32U0 series.xlsx
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AM17" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN17" s="4" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AM18" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN18" s="4" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="AM19" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN19" s="4" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AM20" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN20" s="4" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="AM27" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN27" s="4" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AM28" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN28" s="4" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="AM32" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN32" s="4" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AM33" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN33" s="4" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AM34" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN34" s="4" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="AM35" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN35" s="4" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AM36" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN36" s="4" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="AM38" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN38" s="4" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="AM39" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN39" s="4" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AM40" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN40" s="4" t="inlineStr">
@@ -13568,9 +13568,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -13895,9 +13895,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -14222,9 +14222,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -14549,9 +14549,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -16838,9 +16838,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN27" s="6" t="inlineStr">
@@ -17165,9 +17165,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -18473,9 +18473,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">
@@ -18800,9 +18800,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN33" s="8" t="inlineStr">
@@ -19127,9 +19127,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN34" s="6" t="inlineStr">
@@ -19454,9 +19454,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN35" s="6" t="inlineStr">
@@ -19781,9 +19781,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN36" s="6" t="inlineStr">
@@ -20435,9 +20435,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN38" s="8" t="inlineStr">
@@ -20762,9 +20762,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN39" s="6" t="inlineStr">
@@ -21089,9 +21089,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN40" s="6" t="inlineStr">

--- a/product_selector_out/STM32U0 series.xlsx
+++ b/product_selector_out/STM32U0 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM42"/>
+  <dimension ref="A1:BN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.91796875" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u083cc.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u083cc.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u083cc.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u083cc.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u083cc.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -9168,6 +9295,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u073c8.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
@@ -11130,12 +11287,17 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u031c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -11156,16 +11318,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -11178,6 +11338,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -11197,7 +11358,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -11245,7 +11408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM42"/>
+  <dimension ref="A1:BN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11313,6 +11476,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11646,6 +11810,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -11741,6 +11910,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -12063,7 +12233,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12390,7 +12565,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12717,7 +12897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13044,7 +13229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13371,7 +13561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13698,7 +13893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14025,7 +14225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14352,7 +14557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14679,7 +14889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15006,7 +15221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15333,7 +15553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15660,7 +15885,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15987,7 +16217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16314,7 +16549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16641,7 +16881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16968,7 +17213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17295,7 +17545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17622,7 +17877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17949,7 +18209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18276,7 +18541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18603,7 +18873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18930,7 +19205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19257,7 +19537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19584,7 +19869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19911,7 +20201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20238,7 +20533,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20565,7 +20865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20892,7 +21197,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21219,7 +21529,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21546,7 +21861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21873,7 +22193,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21881,8 +22206,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
